--- a/docs/Диаграмма Ганта Серебряков.xlsx
+++ b/docs/Диаграмма Ганта Серебряков.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="65">
   <si>
     <t>Диаграмма Ганта: сервис агрегации вакансий с матчингом по резюме</t>
   </si>
@@ -78,27 +78,27 @@
     <t>Коннектор к источнику №1 (API/скрейпинг) + обработка сбоев источника</t>
   </si>
   <si>
+    <t>Инфраструктура очередей (брокер, воркеры, retry/DLQ)</t>
+  </si>
+  <si>
+    <t>Дедупликация вакансий (fuzzy matching)</t>
+  </si>
+  <si>
+    <t>Не начато</t>
+  </si>
+  <si>
+    <t>Коннектор к источнику №2 (опционально, для демонстрации расширяемости)</t>
+  </si>
+  <si>
+    <t>ФАЗА 2. Backend: резюме и матчинг по ключевым словам</t>
+  </si>
+  <si>
+    <t>Загрузка и парсинг резюме (PDF/текст → чистый текст)</t>
+  </si>
+  <si>
     <t>В работе</t>
   </si>
   <si>
-    <t>Инфраструктура очередей (брокер, воркеры, retry/DLQ)</t>
-  </si>
-  <si>
-    <t>Дедупликация вакансий (fuzzy matching)</t>
-  </si>
-  <si>
-    <t>Не начато</t>
-  </si>
-  <si>
-    <t>Коннектор к источнику №2 (опционально, для демонстрации расширяемости)</t>
-  </si>
-  <si>
-    <t>ФАЗА 2. Backend: резюме и матчинг по ключевым словам</t>
-  </si>
-  <si>
-    <t>Загрузка и парсинг резюме (PDF/текст → чистый текст)</t>
-  </si>
-  <si>
     <t>Словарь навыков и синонимов (postgres = postgresql, js = javascript)</t>
   </si>
   <si>
@@ -165,7 +165,7 @@
     <t>Настройки уведомлений и порога релевантности</t>
   </si>
   <si>
-    <t>ФАЗА 4. Публичные ссылки (фича преподавателя)</t>
+    <t>ФАЗА 4. Публичные ссылки</t>
   </si>
   <si>
     <t>Модель share_links: токены (только хеш), белый список полей, срок, отзыв</t>
@@ -1774,7 +1774,7 @@
         <v>3</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H8" s="20" t="s">
         <v>14</v>
@@ -1782,7 +1782,9 @@
       <c r="I8" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="J8" s="20"/>
+      <c r="J8" s="20" t="s">
+        <v>14</v>
+      </c>
       <c r="K8" s="20"/>
       <c r="L8" s="20"/>
       <c r="M8" s="20"/>
@@ -1798,7 +1800,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" s="19" t="s">
         <v>12</v>
@@ -1814,11 +1816,15 @@
         <v>3</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H9" s="20"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="20"/>
+      <c r="I9" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" s="20" t="s">
+        <v>14</v>
+      </c>
       <c r="K9" s="20"/>
       <c r="L9" s="20"/>
       <c r="M9" s="20"/>
@@ -1834,7 +1840,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" s="19" t="s">
         <v>12</v>
@@ -1850,7 +1856,7 @@
         <v>5</v>
       </c>
       <c r="G10" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H10" s="20"/>
       <c r="I10" s="20"/>
@@ -1870,7 +1876,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11" s="19" t="s">
         <v>12</v>
@@ -1886,7 +1892,7 @@
         <v>9</v>
       </c>
       <c r="G11" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H11" s="20"/>
       <c r="I11" s="20"/>
@@ -1904,7 +1910,7 @@
     <row r="12" spans="1:19">
       <c r="A12" s="15"/>
       <c r="B12" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12" s="15"/>
       <c r="D12" s="15"/>
@@ -1929,7 +1935,7 @@
         <v>6</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13" s="19" t="s">
         <v>12</v>
@@ -1945,7 +1951,7 @@
         <v>4</v>
       </c>
       <c r="G13" s="19" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H13" s="20"/>
       <c r="I13" s="20"/>
@@ -1981,7 +1987,7 @@
         <v>5</v>
       </c>
       <c r="G14" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H14" s="20"/>
       <c r="I14" s="20"/>
@@ -2017,7 +2023,7 @@
         <v>6</v>
       </c>
       <c r="G15" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H15" s="20"/>
       <c r="I15" s="20"/>
@@ -2053,7 +2059,7 @@
         <v>7</v>
       </c>
       <c r="G16" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H16" s="20"/>
       <c r="I16" s="20"/>
@@ -2089,7 +2095,7 @@
         <v>6</v>
       </c>
       <c r="G17" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H17" s="20"/>
       <c r="I17" s="20"/>
@@ -2125,7 +2131,7 @@
         <v>8</v>
       </c>
       <c r="G18" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H18" s="20"/>
       <c r="I18" s="20"/>
@@ -2161,7 +2167,7 @@
         <v>9</v>
       </c>
       <c r="G19" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H19" s="20"/>
       <c r="I19" s="20"/>
@@ -2197,7 +2203,7 @@
         <v>9</v>
       </c>
       <c r="G20" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H20" s="20"/>
       <c r="I20" s="20"/>
@@ -2233,7 +2239,7 @@
         <v>10</v>
       </c>
       <c r="G21" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H21" s="20"/>
       <c r="I21" s="20"/>
@@ -2269,7 +2275,7 @@
         <v>11</v>
       </c>
       <c r="G22" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H22" s="20"/>
       <c r="I22" s="20"/>
@@ -2305,7 +2311,7 @@
         <v>8</v>
       </c>
       <c r="G23" s="19" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H23" s="20"/>
       <c r="I23" s="20"/>
@@ -2404,11 +2410,15 @@
         <v>3</v>
       </c>
       <c r="G26" s="19" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
+      <c r="I26" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="J26" s="20" t="s">
+        <v>14</v>
+      </c>
       <c r="K26" s="20"/>
       <c r="L26" s="20"/>
       <c r="M26" s="20"/>
@@ -2440,7 +2450,7 @@
         <v>4</v>
       </c>
       <c r="G27" s="19" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H27" s="20"/>
       <c r="I27" s="20"/>
@@ -2476,7 +2486,7 @@
         <v>5</v>
       </c>
       <c r="G28" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H28" s="20"/>
       <c r="I28" s="20"/>
@@ -2512,7 +2522,7 @@
         <v>7</v>
       </c>
       <c r="G29" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H29" s="20"/>
       <c r="I29" s="20"/>
@@ -2548,7 +2558,7 @@
         <v>7</v>
       </c>
       <c r="G30" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H30" s="20"/>
       <c r="I30" s="20"/>
@@ -2584,7 +2594,7 @@
         <v>8</v>
       </c>
       <c r="G31" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H31" s="20"/>
       <c r="I31" s="20"/>
@@ -2620,7 +2630,7 @@
         <v>9</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H32" s="20"/>
       <c r="I32" s="20"/>
@@ -2656,7 +2666,7 @@
         <v>10</v>
       </c>
       <c r="G33" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H33" s="20"/>
       <c r="I33" s="20"/>
@@ -2692,7 +2702,7 @@
         <v>10</v>
       </c>
       <c r="G34" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H34" s="20"/>
       <c r="I34" s="20"/>
@@ -2751,7 +2761,7 @@
         <v>10</v>
       </c>
       <c r="G36" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H36" s="20"/>
       <c r="I36" s="20"/>
@@ -2787,7 +2797,7 @@
         <v>11</v>
       </c>
       <c r="G37" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H37" s="20"/>
       <c r="I37" s="20"/>
@@ -2823,7 +2833,7 @@
         <v>11</v>
       </c>
       <c r="G38" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H38" s="20"/>
       <c r="I38" s="20"/>
@@ -2859,7 +2869,7 @@
         <v>11</v>
       </c>
       <c r="G39" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H39" s="20"/>
       <c r="I39" s="20"/>
@@ -2918,10 +2928,12 @@
         <v>10</v>
       </c>
       <c r="G41" s="19" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H41" s="20"/>
-      <c r="I41" s="20"/>
+      <c r="I41" s="20" t="s">
+        <v>14</v>
+      </c>
       <c r="J41" s="20"/>
       <c r="K41" s="20"/>
       <c r="L41" s="20"/>
@@ -2954,7 +2966,7 @@
         <v>9</v>
       </c>
       <c r="G42" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H42" s="20"/>
       <c r="I42" s="20"/>
@@ -2990,7 +3002,7 @@
         <v>10</v>
       </c>
       <c r="G43" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H43" s="20"/>
       <c r="I43" s="20"/>
@@ -3026,7 +3038,7 @@
         <v>10</v>
       </c>
       <c r="G44" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H44" s="20"/>
       <c r="I44" s="20"/>
@@ -3062,7 +3074,7 @@
         <v>11</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H45" s="20"/>
       <c r="I45" s="20"/>
@@ -3098,7 +3110,7 @@
         <v>11</v>
       </c>
       <c r="G46" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H46" s="20"/>
       <c r="I46" s="20"/>
@@ -3134,7 +3146,7 @@
         <v>12</v>
       </c>
       <c r="G47" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H47" s="20"/>
       <c r="I47" s="20"/>
@@ -3170,12 +3182,14 @@
         <v>12</v>
       </c>
       <c r="G48" s="19" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H48" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="I48" s="20"/>
+      <c r="I48" s="20" t="s">
+        <v>14</v>
+      </c>
       <c r="J48" s="20"/>
       <c r="K48" s="20"/>
       <c r="L48" s="20"/>

--- a/docs/Диаграмма Ганта Серебряков.xlsx
+++ b/docs/Диаграмма Ганта Серебряков.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="13980" tabRatio="500"/>
+    <workbookView windowWidth="21600" windowHeight="10455" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Gantt" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="65">
   <si>
     <t>Диаграмма Ганта: сервис агрегации вакансий с матчингом по резюме</t>
   </si>
@@ -1549,17 +1549,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:S48"/>
-  <sheetFormatPr defaultColWidth="8.67619047619048" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.67256637168142" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="62" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
     <col min="4" max="6" width="9" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="19" width="4.5047619047619" customWidth="1"/>
+    <col min="8" max="19" width="4.50442477876106" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" spans="1:19">
+    <row r="1" ht="17.6" spans="1:19">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>9</v>
       </c>
       <c r="H5" s="14">
-        <f t="shared" ref="H5:S5" si="0" xml:space="preserve">$C$2+7*(H$4-1)</f>
+        <f t="shared" ref="H5:S5" si="0">$C$2+7*(H$4-1)</f>
         <v>46297</v>
       </c>
       <c r="I5" s="14">
@@ -1730,7 +1730,7 @@
         <v>2</v>
       </c>
       <c r="F7" s="17">
-        <f xml:space="preserve">D7+E7-1</f>
+        <f>D7+E7-1</f>
         <v>2</v>
       </c>
       <c r="G7" s="19" t="s">
@@ -1770,7 +1770,7 @@
         <v>3</v>
       </c>
       <c r="F8" s="17">
-        <f xml:space="preserve">D8+E8-1</f>
+        <f>D8+E8-1</f>
         <v>3</v>
       </c>
       <c r="G8" s="19" t="s">
@@ -1812,7 +1812,7 @@
         <v>2</v>
       </c>
       <c r="F9" s="17">
-        <f xml:space="preserve">D9+E9-1</f>
+        <f>D9+E9-1</f>
         <v>3</v>
       </c>
       <c r="G9" s="19" t="s">
@@ -1852,7 +1852,7 @@
         <v>2</v>
       </c>
       <c r="F10" s="17">
-        <f xml:space="preserve">D10+E10-1</f>
+        <f>D10+E10-1</f>
         <v>5</v>
       </c>
       <c r="G10" s="19" t="s">
@@ -1888,7 +1888,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="17">
-        <f xml:space="preserve">D11+E11-1</f>
+        <f>D11+E11-1</f>
         <v>9</v>
       </c>
       <c r="G11" s="19" t="s">
@@ -1947,7 +1947,7 @@
         <v>2</v>
       </c>
       <c r="F13" s="17">
-        <f t="shared" ref="F13:F23" si="1" xml:space="preserve">D13+E13-1</f>
+        <f t="shared" ref="F13:F23" si="1">D13+E13-1</f>
         <v>4</v>
       </c>
       <c r="G13" s="19" t="s">
@@ -2366,7 +2366,7 @@
         <v>2</v>
       </c>
       <c r="F25" s="17">
-        <f t="shared" ref="F25:F34" si="2" xml:space="preserve">D25+E25-1</f>
+        <f t="shared" ref="F25:F34" si="2">D25+E25-1</f>
         <v>2</v>
       </c>
       <c r="G25" s="19" t="s">
@@ -2450,12 +2450,16 @@
         <v>4</v>
       </c>
       <c r="G27" s="19" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H27" s="20"/>
       <c r="I27" s="20"/>
-      <c r="J27" s="20"/>
-      <c r="K27" s="20"/>
+      <c r="J27" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K27" s="20" t="s">
+        <v>14</v>
+      </c>
       <c r="L27" s="20"/>
       <c r="M27" s="20"/>
       <c r="N27" s="20"/>
@@ -2486,7 +2490,7 @@
         <v>5</v>
       </c>
       <c r="G28" s="19" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H28" s="20"/>
       <c r="I28" s="20"/>
@@ -2757,7 +2761,7 @@
         <v>2</v>
       </c>
       <c r="F36" s="17">
-        <f xml:space="preserve">D36+E36-1</f>
+        <f>D36+E36-1</f>
         <v>10</v>
       </c>
       <c r="G36" s="19" t="s">
@@ -2793,7 +2797,7 @@
         <v>2</v>
       </c>
       <c r="F37" s="17">
-        <f xml:space="preserve">D37+E37-1</f>
+        <f>D37+E37-1</f>
         <v>11</v>
       </c>
       <c r="G37" s="19" t="s">
@@ -2829,7 +2833,7 @@
         <v>2</v>
       </c>
       <c r="F38" s="17">
-        <f xml:space="preserve">D38+E38-1</f>
+        <f>D38+E38-1</f>
         <v>11</v>
       </c>
       <c r="G38" s="19" t="s">
@@ -2865,7 +2869,7 @@
         <v>1</v>
       </c>
       <c r="F39" s="17">
-        <f xml:space="preserve">D39+E39-1</f>
+        <f>D39+E39-1</f>
         <v>11</v>
       </c>
       <c r="G39" s="19" t="s">
@@ -2924,7 +2928,7 @@
         <v>9</v>
       </c>
       <c r="F41" s="17">
-        <f t="shared" ref="F41:F48" si="3" xml:space="preserve">D41+E41-1</f>
+        <f t="shared" ref="F41:F48" si="3">D41+E41-1</f>
         <v>10</v>
       </c>
       <c r="G41" s="19" t="s">
@@ -3239,14 +3243,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.67619047619048" defaultRowHeight="15" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="8.67256637168142" defaultRowHeight="14.25" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" spans="1:3">
+    <row r="1" ht="15" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>60</v>
       </c>
@@ -3267,11 +3271,11 @@
         <v>12</v>
       </c>
       <c r="B4" s="3">
-        <f xml:space="preserve">SUMIFS(Gantt!$E$6:$E$48,Gantt!$C$6:$C$48,A4)</f>
+        <f>SUMIFS(Gantt!$E$6:$E$48,Gantt!$C$6:$C$48,A4)</f>
         <v>45</v>
       </c>
       <c r="C4" s="4">
-        <f xml:space="preserve">IF($B$7=0,0,B4/$B$7)</f>
+        <f>IF($B$7=0,0,B4/$B$7)</f>
         <v>0.454545454545455</v>
       </c>
     </row>
@@ -3280,11 +3284,11 @@
         <v>35</v>
       </c>
       <c r="B5" s="3">
-        <f xml:space="preserve">SUMIFS(Gantt!$E$6:$E$48,Gantt!$C$6:$C$48,A5)</f>
+        <f>SUMIFS(Gantt!$E$6:$E$48,Gantt!$C$6:$C$48,A5)</f>
         <v>25</v>
       </c>
       <c r="C5" s="4">
-        <f xml:space="preserve">IF($B$7=0,0,B5/$B$7)</f>
+        <f>IF($B$7=0,0,B5/$B$7)</f>
         <v>0.252525252525253</v>
       </c>
     </row>
@@ -3293,11 +3297,11 @@
         <v>52</v>
       </c>
       <c r="B6" s="3">
-        <f xml:space="preserve">SUMIFS(Gantt!$E$6:$E$48,Gantt!$C$6:$C$48,A6)</f>
+        <f>SUMIFS(Gantt!$E$6:$E$48,Gantt!$C$6:$C$48,A6)</f>
         <v>29</v>
       </c>
       <c r="C6" s="4">
-        <f xml:space="preserve">IF($B$7=0,0,B6/$B$7)</f>
+        <f>IF($B$7=0,0,B6/$B$7)</f>
         <v>0.292929292929293</v>
       </c>
     </row>
@@ -3306,11 +3310,11 @@
         <v>63</v>
       </c>
       <c r="B7" s="5">
-        <f xml:space="preserve">SUM(B4:B6)</f>
+        <f>SUM(B4:B6)</f>
         <v>99</v>
       </c>
       <c r="C7" s="6">
-        <f xml:space="preserve">SUM(C4:C6)</f>
+        <f>SUM(C4:C6)</f>
         <v>1</v>
       </c>
     </row>

--- a/docs/Диаграмма Ганта Серебряков.xlsx
+++ b/docs/Диаграмма Ганта Серебряков.xlsx
@@ -1642,7 +1642,7 @@
         <v>9</v>
       </c>
       <c r="H5" s="14">
-        <f t="shared" ref="H5:S5" si="0" xml:space="preserve">$C$2+7*(H$4-1)</f>
+        <f t="shared" ref="H5:S5" si="0">$C$2+7*(H$4-1)</f>
         <v>46297</v>
       </c>
       <c r="I5" s="14">
@@ -1730,7 +1730,7 @@
         <v>2</v>
       </c>
       <c r="F7" s="17">
-        <f xml:space="preserve">D7+E7-1</f>
+        <f>D7+E7-1</f>
         <v>2</v>
       </c>
       <c r="G7" s="19" t="s">
@@ -1770,7 +1770,7 @@
         <v>3</v>
       </c>
       <c r="F8" s="17">
-        <f xml:space="preserve">D8+E8-1</f>
+        <f>D8+E8-1</f>
         <v>3</v>
       </c>
       <c r="G8" s="19" t="s">
@@ -1812,7 +1812,7 @@
         <v>2</v>
       </c>
       <c r="F9" s="17">
-        <f xml:space="preserve">D9+E9-1</f>
+        <f>D9+E9-1</f>
         <v>3</v>
       </c>
       <c r="G9" s="19" t="s">
@@ -1852,7 +1852,7 @@
         <v>2</v>
       </c>
       <c r="F10" s="17">
-        <f xml:space="preserve">D10+E10-1</f>
+        <f>D10+E10-1</f>
         <v>5</v>
       </c>
       <c r="G10" s="19" t="s">
@@ -1888,7 +1888,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="17">
-        <f xml:space="preserve">D11+E11-1</f>
+        <f>D11+E11-1</f>
         <v>9</v>
       </c>
       <c r="G11" s="19" t="s">
@@ -1947,7 +1947,7 @@
         <v>2</v>
       </c>
       <c r="F13" s="17">
-        <f t="shared" ref="F13:F23" si="1" xml:space="preserve">D13+E13-1</f>
+        <f t="shared" ref="F13:F23" si="1">D13+E13-1</f>
         <v>4</v>
       </c>
       <c r="G13" s="19" t="s">
@@ -2366,7 +2366,7 @@
         <v>2</v>
       </c>
       <c r="F25" s="17">
-        <f t="shared" ref="F25:F34" si="2" xml:space="preserve">D25+E25-1</f>
+        <f t="shared" ref="F25:F34" si="2">D25+E25-1</f>
         <v>2</v>
       </c>
       <c r="G25" s="19" t="s">
@@ -2757,7 +2757,7 @@
         <v>2</v>
       </c>
       <c r="F36" s="17">
-        <f xml:space="preserve">D36+E36-1</f>
+        <f>D36+E36-1</f>
         <v>10</v>
       </c>
       <c r="G36" s="19" t="s">
@@ -2793,7 +2793,7 @@
         <v>2</v>
       </c>
       <c r="F37" s="17">
-        <f xml:space="preserve">D37+E37-1</f>
+        <f>D37+E37-1</f>
         <v>11</v>
       </c>
       <c r="G37" s="19" t="s">
@@ -2829,7 +2829,7 @@
         <v>2</v>
       </c>
       <c r="F38" s="17">
-        <f xml:space="preserve">D38+E38-1</f>
+        <f>D38+E38-1</f>
         <v>11</v>
       </c>
       <c r="G38" s="19" t="s">
@@ -2865,7 +2865,7 @@
         <v>1</v>
       </c>
       <c r="F39" s="17">
-        <f xml:space="preserve">D39+E39-1</f>
+        <f>D39+E39-1</f>
         <v>11</v>
       </c>
       <c r="G39" s="19" t="s">
@@ -2924,7 +2924,7 @@
         <v>9</v>
       </c>
       <c r="F41" s="17">
-        <f t="shared" ref="F41:F48" si="3" xml:space="preserve">D41+E41-1</f>
+        <f t="shared" ref="F41:F48" si="3">D41+E41-1</f>
         <v>10</v>
       </c>
       <c r="G41" s="19" t="s">
@@ -3267,11 +3267,11 @@
         <v>12</v>
       </c>
       <c r="B4" s="3">
-        <f xml:space="preserve">SUMIFS(Gantt!$E$6:$E$48,Gantt!$C$6:$C$48,A4)</f>
+        <f>SUMIFS(Gantt!$E$6:$E$48,Gantt!$C$6:$C$48,A4)</f>
         <v>45</v>
       </c>
       <c r="C4" s="4">
-        <f xml:space="preserve">IF($B$7=0,0,B4/$B$7)</f>
+        <f>IF($B$7=0,0,B4/$B$7)</f>
         <v>0.454545454545455</v>
       </c>
     </row>
@@ -3280,11 +3280,11 @@
         <v>35</v>
       </c>
       <c r="B5" s="3">
-        <f xml:space="preserve">SUMIFS(Gantt!$E$6:$E$48,Gantt!$C$6:$C$48,A5)</f>
+        <f>SUMIFS(Gantt!$E$6:$E$48,Gantt!$C$6:$C$48,A5)</f>
         <v>25</v>
       </c>
       <c r="C5" s="4">
-        <f xml:space="preserve">IF($B$7=0,0,B5/$B$7)</f>
+        <f>IF($B$7=0,0,B5/$B$7)</f>
         <v>0.252525252525253</v>
       </c>
     </row>
@@ -3293,11 +3293,11 @@
         <v>52</v>
       </c>
       <c r="B6" s="3">
-        <f xml:space="preserve">SUMIFS(Gantt!$E$6:$E$48,Gantt!$C$6:$C$48,A6)</f>
+        <f>SUMIFS(Gantt!$E$6:$E$48,Gantt!$C$6:$C$48,A6)</f>
         <v>29</v>
       </c>
       <c r="C6" s="4">
-        <f xml:space="preserve">IF($B$7=0,0,B6/$B$7)</f>
+        <f>IF($B$7=0,0,B6/$B$7)</f>
         <v>0.292929292929293</v>
       </c>
     </row>
@@ -3306,11 +3306,11 @@
         <v>63</v>
       </c>
       <c r="B7" s="5">
-        <f xml:space="preserve">SUM(B4:B6)</f>
+        <f>SUM(B4:B6)</f>
         <v>99</v>
       </c>
       <c r="C7" s="6">
-        <f xml:space="preserve">SUM(C4:C6)</f>
+        <f>SUM(C4:C6)</f>
         <v>1</v>
       </c>
     </row>

--- a/docs/Диаграмма Ганта Серебряков.xlsx
+++ b/docs/Диаграмма Ганта Серебряков.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21600" windowHeight="10455" tabRatio="500"/>
+    <workbookView windowWidth="28800" windowHeight="13980" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Gantt" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="65">
   <si>
     <t>Диаграмма Ганта: сервис агрегации вакансий с матчингом по резюме</t>
   </si>
@@ -84,19 +84,19 @@
     <t>Дедупликация вакансий (fuzzy matching)</t>
   </si>
   <si>
+    <t>В работе</t>
+  </si>
+  <si>
+    <t>Коннектор к источнику №2 (опционально, для демонстрации расширяемости)</t>
+  </si>
+  <si>
     <t>Не начато</t>
   </si>
   <si>
-    <t>Коннектор к источнику №2 (опционально, для демонстрации расширяемости)</t>
-  </si>
-  <si>
     <t>ФАЗА 2. Backend: резюме и матчинг по ключевым словам</t>
   </si>
   <si>
     <t>Загрузка и парсинг резюме (PDF/текст → чистый текст)</t>
-  </si>
-  <si>
-    <t>В работе</t>
   </si>
   <si>
     <t>Словарь навыков и синонимов (postgres = postgresql, js = javascript)</t>
@@ -1549,17 +1549,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:S48"/>
-  <sheetFormatPr defaultColWidth="8.67256637168142" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="8.67619047619048" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="62" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
     <col min="4" max="6" width="9" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="19" width="4.50442477876106" customWidth="1"/>
+    <col min="8" max="19" width="4.5047619047619" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.6" spans="1:19">
+    <row r="1" ht="18" spans="1:19">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1892,7 +1892,7 @@
         <v>9</v>
       </c>
       <c r="G11" s="19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H11" s="20"/>
       <c r="I11" s="20"/>
@@ -1910,7 +1910,7 @@
     <row r="12" spans="1:19">
       <c r="A12" s="15"/>
       <c r="B12" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" s="15"/>
       <c r="D12" s="15"/>
@@ -1935,7 +1935,7 @@
         <v>6</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" s="19" t="s">
         <v>12</v>
@@ -1951,12 +1951,16 @@
         <v>4</v>
       </c>
       <c r="G13" s="19" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H13" s="20"/>
       <c r="I13" s="20"/>
-      <c r="J13" s="20"/>
-      <c r="K13" s="20"/>
+      <c r="J13" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K13" s="20" t="s">
+        <v>14</v>
+      </c>
       <c r="L13" s="20"/>
       <c r="M13" s="20"/>
       <c r="N13" s="20"/>
@@ -2023,7 +2027,7 @@
         <v>6</v>
       </c>
       <c r="G15" s="19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H15" s="20"/>
       <c r="I15" s="20"/>
@@ -2059,7 +2063,7 @@
         <v>7</v>
       </c>
       <c r="G16" s="19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H16" s="20"/>
       <c r="I16" s="20"/>
@@ -2095,7 +2099,7 @@
         <v>6</v>
       </c>
       <c r="G17" s="19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H17" s="20"/>
       <c r="I17" s="20"/>
@@ -2131,7 +2135,7 @@
         <v>8</v>
       </c>
       <c r="G18" s="19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H18" s="20"/>
       <c r="I18" s="20"/>
@@ -2167,7 +2171,7 @@
         <v>9</v>
       </c>
       <c r="G19" s="19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H19" s="20"/>
       <c r="I19" s="20"/>
@@ -2203,7 +2207,7 @@
         <v>9</v>
       </c>
       <c r="G20" s="19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H20" s="20"/>
       <c r="I20" s="20"/>
@@ -2239,7 +2243,7 @@
         <v>10</v>
       </c>
       <c r="G21" s="19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H21" s="20"/>
       <c r="I21" s="20"/>
@@ -2275,7 +2279,7 @@
         <v>11</v>
       </c>
       <c r="G22" s="19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H22" s="20"/>
       <c r="I22" s="20"/>
@@ -2311,12 +2315,16 @@
         <v>8</v>
       </c>
       <c r="G23" s="19" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H23" s="20"/>
       <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
+      <c r="J23" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="K23" s="20" t="s">
+        <v>14</v>
+      </c>
       <c r="L23" s="20"/>
       <c r="M23" s="20"/>
       <c r="N23" s="20"/>
@@ -2490,7 +2498,7 @@
         <v>5</v>
       </c>
       <c r="G28" s="19" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H28" s="20"/>
       <c r="I28" s="20"/>
@@ -2526,7 +2534,7 @@
         <v>7</v>
       </c>
       <c r="G29" s="19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H29" s="20"/>
       <c r="I29" s="20"/>
@@ -2562,7 +2570,7 @@
         <v>7</v>
       </c>
       <c r="G30" s="19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H30" s="20"/>
       <c r="I30" s="20"/>
@@ -2598,7 +2606,7 @@
         <v>8</v>
       </c>
       <c r="G31" s="19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H31" s="20"/>
       <c r="I31" s="20"/>
@@ -2634,7 +2642,7 @@
         <v>9</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H32" s="20"/>
       <c r="I32" s="20"/>
@@ -2670,7 +2678,7 @@
         <v>10</v>
       </c>
       <c r="G33" s="19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H33" s="20"/>
       <c r="I33" s="20"/>
@@ -2706,7 +2714,7 @@
         <v>10</v>
       </c>
       <c r="G34" s="19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H34" s="20"/>
       <c r="I34" s="20"/>
@@ -2765,7 +2773,7 @@
         <v>10</v>
       </c>
       <c r="G36" s="19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H36" s="20"/>
       <c r="I36" s="20"/>
@@ -2801,7 +2809,7 @@
         <v>11</v>
       </c>
       <c r="G37" s="19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H37" s="20"/>
       <c r="I37" s="20"/>
@@ -2837,7 +2845,7 @@
         <v>11</v>
       </c>
       <c r="G38" s="19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H38" s="20"/>
       <c r="I38" s="20"/>
@@ -2873,7 +2881,7 @@
         <v>11</v>
       </c>
       <c r="G39" s="19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H39" s="20"/>
       <c r="I39" s="20"/>
@@ -2932,13 +2940,15 @@
         <v>10</v>
       </c>
       <c r="G41" s="19" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H41" s="20"/>
       <c r="I41" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="J41" s="20"/>
+      <c r="J41" s="20" t="s">
+        <v>14</v>
+      </c>
       <c r="K41" s="20"/>
       <c r="L41" s="20"/>
       <c r="M41" s="20"/>
@@ -2970,7 +2980,7 @@
         <v>9</v>
       </c>
       <c r="G42" s="19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H42" s="20"/>
       <c r="I42" s="20"/>
@@ -3006,7 +3016,7 @@
         <v>10</v>
       </c>
       <c r="G43" s="19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H43" s="20"/>
       <c r="I43" s="20"/>
@@ -3042,7 +3052,7 @@
         <v>10</v>
       </c>
       <c r="G44" s="19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H44" s="20"/>
       <c r="I44" s="20"/>
@@ -3078,7 +3088,7 @@
         <v>11</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H45" s="20"/>
       <c r="I45" s="20"/>
@@ -3114,7 +3124,7 @@
         <v>11</v>
       </c>
       <c r="G46" s="19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H46" s="20"/>
       <c r="I46" s="20"/>
@@ -3150,7 +3160,7 @@
         <v>12</v>
       </c>
       <c r="G47" s="19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H47" s="20"/>
       <c r="I47" s="20"/>
@@ -3186,7 +3196,7 @@
         <v>12</v>
       </c>
       <c r="G48" s="19" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H48" s="20" t="s">
         <v>14</v>
@@ -3194,7 +3204,9 @@
       <c r="I48" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="J48" s="20"/>
+      <c r="J48" s="20" t="s">
+        <v>14</v>
+      </c>
       <c r="K48" s="20"/>
       <c r="L48" s="20"/>
       <c r="M48" s="20"/>
@@ -3243,14 +3255,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.67256637168142" defaultRowHeight="14.25" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="8.67619047619048" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:3">
+    <row r="1" ht="15.75" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>60</v>
       </c>
